--- a/株式会社ミドリメディカル/株式会社ミドリメディカル_案件マスター_260819.xlsx
+++ b/株式会社ミドリメディカル/株式会社ミドリメディカル_案件マスター_260819.xlsx
@@ -17204,7 +17204,9 @@
         <f>'BS(借方)'!E48</f>
         <v>985404</v>
       </c>
-      <c r="D48" s="234"/>
+      <c r="D48" s="234">
+        <f>-C48</f>
+      </c>
       <c r="E48" s="263">
         <f t="shared" ref="E48:E59" si="3">C48+D48</f>
         <v>985404</v>
@@ -17367,7 +17369,7 @@
         <v>0</v>
       </c>
       <c r="D60" s="320">
-        <v>0</v>
+        <f>ROUND(MAX(0,-('修正BS(借方)'!D5+'修正BS(借方)'!D20+'修正BS(借方)'!D56-('修正BS(貸方) '!D5+'修正BS(貸方) '!D18))*0.34),0)</f>
       </c>
       <c r="E60" s="321">
         <f>C60+D60</f>
@@ -17726,11 +17728,11 @@
     <row r="4" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="75" t="inlineStr">
         <is>
-          <t>未収入金（相手先別内訳 未受領）</t>
+          <t>社会保険診療報酬支払基金（神奈川県）</t>
         </is>
       </c>
       <c r="C4" s="296">
-        <v>52401281</v>
+        <v>35166706</v>
       </c>
       <c r="D4" s="296">
         <v>0</v>
@@ -17741,29 +17743,53 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>債権年齢表・補助元帳が未受領のため個別の回収可能性判断は未実施。帳簿価額により評価する（要確認）。なお貸倒引当金524千円は全額戻入。総資産の約33%を占める重要科目。</t>
+          <t>診療報酬の請求債権。公的保険者に対する債権であり貸倒リスクは実質的にないため帳簿価額により評価する。</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="75"/>
-      <c r="C5" s="297"/>
-      <c r="D5" s="297"/>
+      <c r="B5" s="75" t="inlineStr">
+        <is>
+          <t>神奈川県国民健康保険団体連合会</t>
+        </is>
+      </c>
+      <c r="C5" s="297">
+        <v>16411998</v>
+      </c>
+      <c r="D5" s="297">
+        <v>0</v>
+      </c>
       <c r="E5" s="297">
         <f t="shared" ref="E5:E7" si="0">SUM(C5,D5)</f>
         <v>3087.5</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>診療報酬16,270,584円及び介護給付費141,414円。同上。</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="75"/>
-      <c r="C6" s="297"/>
-      <c r="D6" s="297"/>
+      <c r="B6" s="75" t="inlineStr">
+        <is>
+          <t>その他（㈱パーク24・窓口未収金等）</t>
+        </is>
+      </c>
+      <c r="C6" s="297">
+        <v>822577</v>
+      </c>
+      <c r="D6" s="297">
+        <v>0</v>
+      </c>
       <c r="E6" s="297">
         <f t="shared" si="0"/>
         <v>8287</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>㈱パーク24 546千円ほか小口7件。内容は要確認。</t>
+        </is>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="416"/>
@@ -17821,7 +17847,7 @@
     <row r="14" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="417" t="inlineStr">
         <is>
-          <t>商品（品目別内訳 未受領）</t>
+          <t>商品（薬品等）</t>
         </is>
       </c>
       <c r="C14" s="300">
@@ -17835,14 +17861,14 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>棚卸資産明細・滞留在庫の状況が未確認のため帳簿価額により評価する（要確認）。評価方法は最終仕入原価法。</t>
+          <t>内訳書上は「薬品等（明細書会社保存）」の一括表示。品目別明細・使用期限別の滞留状況が未確認のため帳簿価額により評価する（要確認）。評価方法は最終仕入原価法。</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="418" t="inlineStr">
         <is>
-          <t>貯蔵品</t>
+          <t>貯蔵品（薬袋等）</t>
         </is>
       </c>
       <c r="C15" s="300">
@@ -17949,7 +17975,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>固定資産台帳が未受領のため個別資産の償却過不足の検証は未実施。税法基準（定率法・建物附属設備は定額法、ソフトウェアは定額法）により継続的に償却されており、帳簿価額により評価する（要確認）。</t>
+          <t>固定資産台帳が未受領のため個別資産の償却過不足の検証は未実施。税法基準（定率法・建物附属設備は定額法、ソフトウェアは定額法）により継続的に償却されており、帳簿価額により評価する（要確認）。店舗はいずれも賃借であり、有形固定資産の大宗は内装造作と推察される。</t>
         </is>
       </c>
     </row>
@@ -18084,7 +18110,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>対象会社は土地・建物等の不動産を保有していない（令和7年12月期BSに計上なし、本社等は賃借）。したがって不動産の時価評価は実施していない。</t>
+          <t>対象会社は土地・建物等の不動産を保有していない。店舗3件・駐車場4件はいずれも賃借（地代家賃等の内訳書により確認）。したがって不動産の時価評価は実施していない。</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18210,7 @@
     <row r="4" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="75" t="inlineStr">
         <is>
-          <t>該当なし</t>
+          <t>中小企業倒産防止共済（簿外）</t>
         </is>
       </c>
       <c r="C4" s="296">
@@ -18199,16 +18225,28 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>令和7年12月期BSに保険積立金の計上はない。簿外の積立（経営セーフティ共済等）の有無は未確認（要確認）。</t>
+          <t>令和7年12月期BSに保険積立金の計上はないが、雑益の内訳書に「倒産防止共済金 前納減額金 9,720円」の計上があり、掛金を全額損金算入している簿外の積立が存在すると認められる。解約手当金額（最大800万円）は時価純資産の加算要素となるため、加入時期・掛金月額・納付済掛金総額を要確認。金額が特定できないため本評価では未計上とする。</t>
         </is>
       </c>
     </row>
     <row r="5" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="421"/>
-      <c r="C5" s="297"/>
+      <c r="B5" s="421" t="inlineStr">
+        <is>
+          <t>生命保険等</t>
+        </is>
+      </c>
+      <c r="C5" s="297">
+        <v>0</v>
+      </c>
       <c r="D5" s="297"/>
-      <c r="E5" s="297"/>
-      <c r="F5" s="4"/>
+      <c r="E5" s="297">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>保険料1,603千円（令和7年12月期）の内訳・保険証券が未受領のため、掛捨て以外の積立性保険の有無は未確認（要確認）。</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="422"/>
@@ -18305,7 +18343,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>令和7年12月期BSに有価証券・投資有価証券の計上はない。</t>
+          <t>令和7年12月期BSに有価証券・投資有価証券の計上はない。貸付金及び受取利息の内訳書上、役員貸付金・従業員貸付金の計上もない。</t>
         </is>
       </c>
     </row>
@@ -18736,7 +18774,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="256">
-        <f>ROUND(('修正BS(借方)'!D61-'修正BS(借方)'!D60-(D5+D18))*0.34,0)</f>
+        <f>ROUND(MAX(0,('修正BS(借方)'!D5+'修正BS(借方)'!D20+'修正BS(借方)'!D56-('修正BS(貸方) '!D5+'修正BS(貸方) '!D18))*0.34),0)</f>
       </c>
       <c r="E27" s="264">
         <f>C27+D27</f>
@@ -19454,7 +19492,7 @@
     <row r="11" spans="2:7" ht="31.7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="354" t="inlineStr">
         <is>
-          <t>賞与支給規程・支給月が未確認のため賞与引当不足額は算定不能。販管費上の賞与は3,197千円（令和7年12月期）。要確認事項として整理し、本評価では未計上とする。</t>
+          <t>未払金の内訳書に「港北年金事務所 2,349,413円（11月分・賞与分社会保険料）」の計上があり、賞与に係る社会保険料は未払計上されている。賞与支給規程・支給月が未確認のため賞与引当不足額は算定不能。本評価では未計上とする（要確認）。</t>
         </is>
       </c>
     </row>
@@ -19676,12 +19714,16 @@
       <c r="E4" s="296">
         <f>-D4*0.34</f>
       </c>
-      <c r="F4" s="360"/>
+      <c r="F4" s="360" t="inlineStr">
+        <is>
+          <t>全額戻入。将来加算一時差異</t>
+        </is>
+      </c>
     </row>
     <row r="5" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="421" t="inlineStr">
         <is>
-          <t>未収入金</t>
+          <t>長期前払費用</t>
         </is>
       </c>
       <c r="C5" s="362" t="inlineStr">
@@ -19689,20 +19731,22 @@
           <t>〇</t>
         </is>
       </c>
-      <c r="D5" s="297"/>
+      <c r="D5" s="297">
+        <v>-985404</v>
+      </c>
       <c r="E5" s="297">
         <f>-D5*0.34</f>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>債権年齢表・補助元帳が未受領のため簿価評価（要確認）</t>
+          <t>賃貸借契約の更新料の未償却分を全額控除。将来減算一時差異</t>
         </is>
       </c>
     </row>
     <row r="6" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="421" t="inlineStr">
         <is>
-          <t>商品・貯蔵品</t>
+          <t>未収入金</t>
         </is>
       </c>
       <c r="C6" s="362" t="inlineStr">
@@ -19716,14 +19760,14 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>棚卸資産明細・滞留在庫の状況が未確認のため簿価評価（要確認）</t>
+          <t>98.4%が社会保険診療報酬支払基金・国保連に対する債権であり簿価評価</t>
         </is>
       </c>
     </row>
     <row r="7" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="421" t="inlineStr">
         <is>
-          <t>減価償却資産</t>
+          <t>商品・貯蔵品</t>
         </is>
       </c>
       <c r="C7" s="362" t="inlineStr">
@@ -19737,14 +19781,14 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>固定資産台帳が未受領のため償却過不足未検証（要確認）</t>
+          <t>品目別明細・滞留状況が未確認のため簿価評価（要確認）</t>
         </is>
       </c>
     </row>
     <row r="8" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="421" t="inlineStr">
         <is>
-          <t>ソフトウェア</t>
+          <t>減価償却資産</t>
         </is>
       </c>
       <c r="C8" s="362" t="inlineStr">
@@ -19758,14 +19802,14 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>自社利用の業務システムであり、事業継続を前提に簿価評価</t>
+          <t>固定資産台帳が未受領のため償却過不足未検証（要確認）</t>
         </is>
       </c>
     </row>
     <row r="9" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="421" t="inlineStr">
         <is>
-          <t>差入保証金</t>
+          <t>ソフトウェア</t>
         </is>
       </c>
       <c r="C9" s="362" t="inlineStr">
@@ -19779,14 +19823,14 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>賃貸借契約書の返還条件・原状回復義務が未確認のため簿価評価（要確認）</t>
+          <t>自社利用の業務システムであり、事業継続を前提に簿価評価</t>
         </is>
       </c>
     </row>
     <row r="10" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="421" t="inlineStr">
         <is>
-          <t>長期前払費用</t>
+          <t>差入保証金</t>
         </is>
       </c>
       <c r="C10" s="362" t="inlineStr">
@@ -19800,14 +19844,14 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>内容の内訳が未確認のため簿価評価（要確認）</t>
+          <t>店舗・駐車場7件の保証金。返還条件・原状回復義務が未確認のため簿価評価（要確認）</t>
         </is>
       </c>
     </row>
     <row r="11" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="421" t="inlineStr">
         <is>
-          <t>未払給与（未払残業代）</t>
+          <t>倒産防止共済（簿外）</t>
         </is>
       </c>
       <c r="C11" s="362" t="inlineStr">
@@ -19821,14 +19865,14 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>就業規則・賃金規程が未受領のため未計上（要確認）</t>
+          <t>解約手当金額が未確認のため未計上。判明後は加算要素（要確認）</t>
         </is>
       </c>
     </row>
     <row r="12" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="421" t="inlineStr">
         <is>
-          <t>賞与引当金</t>
+          <t>未払給与（未払残業代）</t>
         </is>
       </c>
       <c r="C12" s="362" t="inlineStr">
@@ -19842,14 +19886,14 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>賞与支給規程・支給月が未確認のため未計上（要確認）</t>
+          <t>就業規則・賃金規程が未受領のため未計上（要確認）</t>
         </is>
       </c>
     </row>
     <row r="13" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="421" t="inlineStr">
         <is>
-          <t>退職給付引当金</t>
+          <t>賞与引当金</t>
         </is>
       </c>
       <c r="C13" s="362" t="inlineStr">
@@ -19863,55 +19907,55 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
+          <t>賞与に係る社会保険料は未払計上済。引当不足額は未確認のため未計上（要確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="421" t="inlineStr">
+        <is>
+          <t>退職給付引当金</t>
+        </is>
+      </c>
+      <c r="C14" s="362" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="D14" s="297"/>
+      <c r="E14" s="297">
+        <f>-D14*0.34</f>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
           <t>退職金規程が未受領のため未計上（要確認）</t>
         </is>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="421"/>
-      <c r="C14" s="362" t="s">
-        <v>329</v>
-      </c>
-      <c r="D14" s="297"/>
-      <c r="E14" s="297">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="4"/>
-    </row>
     <row r="15" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="421"/>
-      <c r="C15" s="362" t="s">
-        <v>329</v>
-      </c>
+      <c r="C15" s="362"/>
       <c r="D15" s="297"/>
       <c r="E15" s="297">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>-D15*0.34</f>
       </c>
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="2:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="421"/>
-      <c r="C16" s="362" t="s">
-        <v>329</v>
-      </c>
+      <c r="C16" s="362"/>
       <c r="D16" s="297"/>
       <c r="E16" s="297">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>-D16*0.34</f>
       </c>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="2:6" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B17" s="416"/>
-      <c r="C17" s="363" t="s">
-        <v>329</v>
-      </c>
+      <c r="C17" s="363"/>
       <c r="D17" s="298"/>
       <c r="E17" s="248">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>-D17*0.34</f>
       </c>
       <c r="F17" s="6"/>
     </row>
@@ -19932,7 +19976,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>本評価における修正項目は貸倒引当金の戻入524千円のみであり、実効税率34%による繰延税金負債178千円を修正貸借対照表上の【繰延税金負債】に計上している。</t>
+          <t>修正額の純額は△461千円（貸倒引当金の戻入524千円－長期前払費用の控除985千円）であり、実効税率34%による繰延税金資産157千円を修正貸借対照表上の【繰延税金資産】に計上している。</t>
         </is>
       </c>
     </row>
@@ -27163,17 +27207,17 @@
     <row r="4" spans="2:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="75" t="inlineStr">
         <is>
-          <t>㈱メディアスホールディングス（3154）</t>
+          <t>㈱アインホールディングス（9627）</t>
         </is>
       </c>
       <c r="C4" s="382" t="inlineStr">
         <is>
-          <t>東京都中央区</t>
+          <t>北海道札幌市</t>
         </is>
       </c>
       <c r="D4" s="382" t="inlineStr">
         <is>
-          <t>医療機器・医療材料の卸売</t>
+          <t>調剤薬局「アイン薬局」の運営、化粧品小売</t>
         </is>
       </c>
       <c r="E4" s="387"/>
@@ -27181,17 +27225,17 @@
     <row r="5" spans="2:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="421" t="inlineStr">
         <is>
-          <t>㈱バイタルケーエスケー・ホールディングス（3151）</t>
+          <t>日本調剤㈱（3341）</t>
         </is>
       </c>
       <c r="C5" s="383" t="inlineStr">
         <is>
-          <t>宮城県仙台市</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="D5" s="383" t="inlineStr">
         <is>
-          <t>医薬品・医療機器の卸売</t>
+          <t>調剤薬局の運営、後発医薬品の製造販売、医療従事者派遣</t>
         </is>
       </c>
       <c r="E5" s="388"/>
@@ -27199,17 +27243,17 @@
     <row r="6" spans="2:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="421" t="inlineStr">
         <is>
-          <t>日本ライフライン㈱（7575）</t>
+          <t>㈱クオールホールディングス（3034）</t>
         </is>
       </c>
       <c r="C6" s="383" t="inlineStr">
         <is>
-          <t>東京都品川区</t>
+          <t>東京都港区</t>
         </is>
       </c>
       <c r="D6" s="383" t="inlineStr">
         <is>
-          <t>医療機器（循環器領域）の輸入・製造・販売</t>
+          <t>調剤薬局「クオール薬局」の運営、医薬品製造受託</t>
         </is>
       </c>
       <c r="E6" s="388"/>
@@ -27217,17 +27261,17 @@
     <row r="7" spans="2:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="421" t="inlineStr">
         <is>
-          <t>㈱シップヘルスケアホールディングス（3360）</t>
+          <t>㈱メディカルシステムネットワーク（4350）</t>
         </is>
       </c>
       <c r="C7" s="383" t="inlineStr">
         <is>
-          <t>大阪府吹田市</t>
+          <t>北海道札幌市</t>
         </is>
       </c>
       <c r="D7" s="383" t="inlineStr">
         <is>
-          <t>医療機器・医療材料の販売、病院向けトータルサービス</t>
+          <t>調剤薬局の運営、医薬品ネットワーク事業</t>
         </is>
       </c>
       <c r="E7" s="388"/>
@@ -27235,17 +27279,17 @@
     <row r="8" spans="2:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="421" t="inlineStr">
         <is>
-          <t>アズワン㈱（7476）</t>
+          <t>㈱ファーマライズホールディングス（2796）</t>
         </is>
       </c>
       <c r="C8" s="383" t="inlineStr">
         <is>
-          <t>大阪府大阪市</t>
+          <t>東京都渋谷区</t>
         </is>
       </c>
       <c r="D8" s="383" t="inlineStr">
         <is>
-          <t>理化学機器・医療介護用品の商社</t>
+          <t>調剤薬局の運営、ヘルスケア関連事業</t>
         </is>
       </c>
       <c r="E8" s="388"/>
@@ -27253,17 +27297,17 @@
     <row r="9" spans="2:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="421" t="inlineStr">
         <is>
-          <t>川本産業㈱（3604）</t>
+          <t>HYUGA PRIMARY CARE㈱（7133）</t>
         </is>
       </c>
       <c r="C9" s="383" t="inlineStr">
         <is>
-          <t>大阪府大阪市</t>
+          <t>福岡県春日市</t>
         </is>
       </c>
       <c r="D9" s="383" t="inlineStr">
         <is>
-          <t>医療用衛生材料・介護用品の製造・販売</t>
+          <t>在宅医療特化型調剤薬局「きらり薬局」の運営</t>
         </is>
       </c>
       <c r="E9" s="388"/>
@@ -27271,17 +27315,17 @@
     <row r="10" spans="2:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="421" t="inlineStr">
         <is>
-          <t>㈱ホギメディカル（3593）</t>
+          <t>㈱ミアヘルサ（7129）</t>
         </is>
       </c>
       <c r="C10" s="383" t="inlineStr">
         <is>
-          <t>東京都港区</t>
+          <t>東京都新宿区</t>
         </is>
       </c>
       <c r="D10" s="383" t="inlineStr">
         <is>
-          <t>手術関連製品・医療用不織布の製造・販売</t>
+          <t>調剤薬局の運営、介護・保育事業</t>
         </is>
       </c>
       <c r="E10" s="388"/>
@@ -27289,17 +27333,17 @@
     <row r="11" spans="2:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="421" t="inlineStr">
         <is>
-          <t>フクダ電子㈱（6960）</t>
+          <t>㈱メディカル一光グループ（3353）</t>
         </is>
       </c>
       <c r="C11" s="383" t="inlineStr">
         <is>
-          <t>東京都文京区</t>
+          <t>三重県四日市市</t>
         </is>
       </c>
       <c r="D11" s="383" t="inlineStr">
         <is>
-          <t>医療電子機器の製造・販売、在宅医療サービス</t>
+          <t>調剤薬局の運営、介護事業</t>
         </is>
       </c>
       <c r="E11" s="388"/>
@@ -27307,17 +27351,17 @@
     <row r="12" spans="2:5" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="421" t="inlineStr">
         <is>
-          <t>㈱メディキット（7749）</t>
+          <t>㈱トーカイ（9729）</t>
         </is>
       </c>
       <c r="C12" s="383" t="inlineStr">
         <is>
-          <t>東京都中央区</t>
+          <t>岐阜県岐阜市</t>
         </is>
       </c>
       <c r="D12" s="383" t="inlineStr">
         <is>
-          <t>医療用穿刺針・カテーテル等の製造・販売</t>
+          <t>調剤薬局の運営、福祉用具レンタル、病院関連サービス</t>
         </is>
       </c>
       <c r="E12" s="388"/>
@@ -27325,17 +27369,17 @@
     <row r="13" spans="2:5" ht="32.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="422" t="inlineStr">
         <is>
-          <t>㈱松風（7979）</t>
+          <t>㈱スギホールディングス（7649）</t>
         </is>
       </c>
       <c r="C13" s="384" t="inlineStr">
         <is>
-          <t>京都府京都市</t>
+          <t>愛知県大府市</t>
         </is>
       </c>
       <c r="D13" s="384" t="inlineStr">
         <is>
-          <t>歯科材料・歯科機器の製造・販売</t>
+          <t>調剤併設型ドラッグストアの運営</t>
         </is>
       </c>
       <c r="E13" s="389"/>
@@ -27364,14 +27408,14 @@
     <row r="17" ht="32.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="381" t="inlineStr">
         <is>
-          <t>※ 上記は事業内容の観点から選定した類似上場会社の候補。対象会社の取扱商品・販売チャネルが未確認のため暫定であり、確認後に見直しを要する。EV/EBITDA倍率は算定日時点の株価等に基づき更新のうえ入力する。</t>
+          <t>※ 勘定科目内訳明細書（棚卸資産＝薬品等、買掛金＝医薬品卸大手、未収入金＝社会保険診療報酬支払基金・国保連）により、対象会社の事業は調剤薬局の運営と認められることから、調剤薬局を主業とする上場会社を選定した。EV/EBITDA倍率は算定日時点の株価等に基づき更新のうえ入力する。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="381" t="inlineStr">
         <is>
-          <t>※ 本評価では、国内中小企業M&amp;Aの実務上のボリュームゾーンである3.0～5.0倍を採用している。</t>
+          <t>※ 本評価では、国内中小企業M&amp;Aの実務上のボリュームゾーンである3.0～5.0倍を採用している。なお対象会社は3店舗の小規模事業者であり、上場会社との規模格差は倍率選定上の考慮事項となる。</t>
         </is>
       </c>
     </row>
@@ -27418,104 +27462,130 @@
       <c r="B3" s="433" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="60" t="s">
-        <v>43</v>
+      <c r="C3" s="60" t="inlineStr">
+        <is>
+          <t>株式会社ミドリメディカル</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="61" t="s">
-        <v>28</v>
+      <c r="C4" s="61" t="inlineStr">
+        <is>
+          <t>要確認（本社所在地の資料未受領）</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="2:3" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="62" t="s">
-        <v>62</v>
+      <c r="C5" s="62" t="inlineStr">
+        <is>
+          <t>調剤薬局3店舗（横浜市緑区中山町、横浜市都筑区仲町台2ヶ所）</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="61" t="s">
-        <v>63</v>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>第9期（令和7年12月期）／12月決算</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="61" t="s">
-        <v>64</v>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>9,000千円</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="61" t="s">
-        <v>44</v>
+      <c r="C8" s="61" t="inlineStr">
+        <is>
+          <t>三河　太一</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="2:3" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="62" t="s">
-        <v>45</v>
+      <c r="C9" s="62" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="61" t="s">
-        <v>46</v>
+      <c r="C10" s="61" t="inlineStr">
+        <is>
+          <t>調剤薬局の運営</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="61" t="s">
-        <v>47</v>
+      <c r="C11" s="61" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
       </c>
     </row>
     <row r="12" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="C12" s="61" t="s">
-        <v>46</v>
+      <c r="C12" s="61" t="inlineStr">
+        <is>
+          <t>薬局開設許可・保険薬局指定（要確認）</t>
+        </is>
       </c>
     </row>
     <row r="13" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="61" t="s">
-        <v>65</v>
+      <c r="C13" s="61" t="inlineStr">
+        <is>
+          <t>357,541千円（令和7年12月期）</t>
+        </is>
       </c>
     </row>
     <row r="14" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="61" t="s">
-        <v>65</v>
+      <c r="C14" s="61" t="inlineStr">
+        <is>
+          <t>18,551千円（令和7年12月期・修正後EBITDA）</t>
+        </is>
       </c>
     </row>
     <row r="15" spans="2:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="61" t="s">
-        <v>48</v>
+      <c r="C15" s="61" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -29566,9 +29636,8 @@
       <c r="E7" s="61"/>
       <c r="F7" s="61"/>
       <c r="G7" s="100"/>
-      <c r="H7" s="59" t="e">
+      <c r="H7" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I7" s="100"/>
       <c r="J7" s="59">
@@ -29589,9 +29658,8 @@
       <c r="E8" s="61"/>
       <c r="F8" s="61"/>
       <c r="G8" s="100"/>
-      <c r="H8" s="59" t="e">
+      <c r="H8" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I8" s="100"/>
       <c r="J8" s="59">
@@ -29612,9 +29680,8 @@
       <c r="E9" s="61"/>
       <c r="F9" s="61"/>
       <c r="G9" s="100"/>
-      <c r="H9" s="59" t="e">
+      <c r="H9" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I9" s="100"/>
       <c r="J9" s="59">
@@ -29635,9 +29702,8 @@
       <c r="E10" s="61"/>
       <c r="F10" s="61"/>
       <c r="G10" s="100"/>
-      <c r="H10" s="59" t="e">
+      <c r="H10" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I10" s="100"/>
       <c r="J10" s="59">
@@ -29658,9 +29724,8 @@
       <c r="E11" s="61"/>
       <c r="F11" s="61"/>
       <c r="G11" s="100"/>
-      <c r="H11" s="59" t="e">
+      <c r="H11" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I11" s="100"/>
       <c r="J11" s="59">
@@ -29681,9 +29746,8 @@
       <c r="E12" s="61"/>
       <c r="F12" s="61"/>
       <c r="G12" s="100"/>
-      <c r="H12" s="59" t="e">
+      <c r="H12" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I12" s="100"/>
       <c r="J12" s="59">
@@ -29704,9 +29768,8 @@
       <c r="E13" s="61"/>
       <c r="F13" s="61"/>
       <c r="G13" s="100"/>
-      <c r="H13" s="59" t="e">
+      <c r="H13" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I13" s="100"/>
       <c r="J13" s="59">
@@ -29727,9 +29790,8 @@
       <c r="E14" s="61"/>
       <c r="F14" s="61"/>
       <c r="G14" s="100"/>
-      <c r="H14" s="59" t="e">
+      <c r="H14" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I14" s="100"/>
       <c r="J14" s="59">
@@ -29881,14 +29943,20 @@
       <c r="B5" s="434">
         <v>1</v>
       </c>
-      <c r="C5" s="61" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" s="61" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="61" t="s">
-        <v>91</v>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>㈱ﾒﾃﾞｨｾｵ</t>
+        </is>
+      </c>
+      <c r="D5" s="61" t="inlineStr">
+        <is>
+          <t>医薬品</t>
+        </is>
+      </c>
+      <c r="E5" s="61" t="inlineStr">
+        <is>
+          <t>東京都中央区</t>
+        </is>
       </c>
       <c r="F5" s="100"/>
       <c r="G5" s="59">
@@ -29902,17 +29970,31 @@
       <c r="K5" s="59">
         <f>IFERROR(J5/J$16,"")</f>
       </c>
-      <c r="L5" s="98" t="s">
-        <v>94</v>
+      <c r="L5" s="98" t="inlineStr">
+        <is>
+          <t>買掛金残高 11,139,951円（R7.12末）</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="2:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="435">
         <v>2</v>
       </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>ｱﾙﾌﾚｯｻ㈱</t>
+        </is>
+      </c>
+      <c r="D6" s="61" t="inlineStr">
+        <is>
+          <t>医薬品</t>
+        </is>
+      </c>
+      <c r="E6" s="61" t="inlineStr">
+        <is>
+          <t>東京都千代田区</t>
+        </is>
+      </c>
       <c r="F6" s="100"/>
       <c r="G6" s="59">
         <f t="shared" ref="G6:G14" si="0">IFERROR(F6/F$16,"")</f>
@@ -29925,103 +30007,159 @@
       <c r="K6" s="59">
         <f t="shared" ref="K6:K14" si="2">IFERROR(J6/J$16,"")</f>
       </c>
-      <c r="L6" s="99"/>
+      <c r="L6" s="99" t="inlineStr">
+        <is>
+          <t>買掛金残高 8,606,699円（R7.12末）</t>
+        </is>
+      </c>
     </row>
     <row r="7" spans="2:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="436">
         <v>3</v>
       </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>㈱ｽｽﾞｹﾝ</t>
+        </is>
+      </c>
+      <c r="D7" s="61" t="inlineStr">
+        <is>
+          <t>医薬品</t>
+        </is>
+      </c>
+      <c r="E7" s="61" t="inlineStr">
+        <is>
+          <t>横浜市緑区</t>
+        </is>
+      </c>
       <c r="F7" s="100"/>
-      <c r="G7" s="59" t="e">
+      <c r="G7" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="H7" s="100"/>
-      <c r="I7" s="59" t="e">
+      <c r="I7" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="J7" s="100"/>
-      <c r="K7" s="59" t="e">
+      <c r="K7" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L7" s="99"/>
+      </c>
+      <c r="L7" s="99" t="inlineStr">
+        <is>
+          <t>買掛金残高 7,011,326円（R7.12末）</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="2:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="435">
         <v>4</v>
       </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
+      <c r="C8" s="61" t="inlineStr">
+        <is>
+          <t>神奈川東和薬品㈱</t>
+        </is>
+      </c>
+      <c r="D8" s="61" t="inlineStr">
+        <is>
+          <t>医薬品</t>
+        </is>
+      </c>
+      <c r="E8" s="61" t="inlineStr">
+        <is>
+          <t>神奈川県高座郡寒川町</t>
+        </is>
+      </c>
       <c r="F8" s="100"/>
-      <c r="G8" s="59" t="e">
+      <c r="G8" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="H8" s="100"/>
-      <c r="I8" s="59" t="e">
+      <c r="I8" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="J8" s="100"/>
-      <c r="K8" s="59" t="e">
+      <c r="K8" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L8" s="99"/>
+      </c>
+      <c r="L8" s="99" t="inlineStr">
+        <is>
+          <t>買掛金残高 68,904円（R7.12末）</t>
+        </is>
+      </c>
     </row>
     <row r="9" spans="2:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="436">
         <v>5</v>
       </c>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
+      <c r="C9" s="61" t="inlineStr">
+        <is>
+          <t>東邦薬品</t>
+        </is>
+      </c>
+      <c r="D9" s="61" t="inlineStr">
+        <is>
+          <t>医薬品</t>
+        </is>
+      </c>
+      <c r="E9" s="61" t="inlineStr">
+        <is>
+          <t>東京都世田谷区</t>
+        </is>
+      </c>
       <c r="F9" s="100"/>
-      <c r="G9" s="59" t="e">
+      <c r="G9" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="H9" s="100"/>
-      <c r="I9" s="59" t="e">
+      <c r="I9" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="J9" s="100"/>
-      <c r="K9" s="59" t="e">
+      <c r="K9" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L9" s="99"/>
+      </c>
+      <c r="L9" s="99" t="inlineStr">
+        <is>
+          <t>買掛金残高 59,368円（R7.12末）</t>
+        </is>
+      </c>
     </row>
     <row r="10" spans="2:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="435">
         <v>6</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
+      <c r="C10" s="61" t="inlineStr">
+        <is>
+          <t>㈱ｼﾝﾘｮｳ</t>
+        </is>
+      </c>
+      <c r="D10" s="61" t="inlineStr">
+        <is>
+          <t>医薬品</t>
+        </is>
+      </c>
+      <c r="E10" s="61" t="inlineStr">
+        <is>
+          <t>東京都豊島区</t>
+        </is>
+      </c>
       <c r="F10" s="100"/>
-      <c r="G10" s="59" t="e">
+      <c r="G10" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="H10" s="100"/>
-      <c r="I10" s="59" t="e">
+      <c r="I10" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="J10" s="100"/>
-      <c r="K10" s="59" t="e">
+      <c r="K10" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L10" s="99"/>
+      </c>
+      <c r="L10" s="99" t="inlineStr">
+        <is>
+          <t>買掛金残高 49,214円（R7.12末）</t>
+        </is>
+      </c>
     </row>
     <row r="11" spans="2:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="436">
@@ -30031,19 +30169,16 @@
       <c r="D11" s="61"/>
       <c r="E11" s="61"/>
       <c r="F11" s="100"/>
-      <c r="G11" s="59" t="e">
+      <c r="G11" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="H11" s="100"/>
-      <c r="I11" s="59" t="e">
+      <c r="I11" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="J11" s="100"/>
-      <c r="K11" s="59" t="e">
+      <c r="K11" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="L11" s="99"/>
     </row>
@@ -30055,19 +30190,16 @@
       <c r="D12" s="61"/>
       <c r="E12" s="61"/>
       <c r="F12" s="100"/>
-      <c r="G12" s="59" t="e">
+      <c r="G12" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="H12" s="100"/>
-      <c r="I12" s="59" t="e">
+      <c r="I12" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="J12" s="100"/>
-      <c r="K12" s="59" t="e">
+      <c r="K12" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="L12" s="99"/>
     </row>
@@ -30079,19 +30211,16 @@
       <c r="D13" s="61"/>
       <c r="E13" s="61"/>
       <c r="F13" s="100"/>
-      <c r="G13" s="59" t="e">
+      <c r="G13" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="H13" s="100"/>
-      <c r="I13" s="59" t="e">
+      <c r="I13" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="J13" s="100"/>
-      <c r="K13" s="59" t="e">
+      <c r="K13" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="L13" s="99"/>
     </row>
@@ -30103,27 +30232,22 @@
       <c r="D14" s="61"/>
       <c r="E14" s="61"/>
       <c r="F14" s="100"/>
-      <c r="G14" s="59" t="e">
+      <c r="G14" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="H14" s="100"/>
-      <c r="I14" s="59" t="e">
+      <c r="I14" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="J14" s="100"/>
-      <c r="K14" s="59" t="e">
+      <c r="K14" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="L14" s="99"/>
     </row>
     <row r="15" spans="2:12" ht="23.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="433"/>
-      <c r="C15" s="93" t="s">
-        <v>89</v>
-      </c>
+      <c r="C15" s="93"/>
       <c r="D15" s="93"/>
       <c r="E15" s="93"/>
       <c r="F15" s="100"/>
@@ -30160,6 +30284,13 @@
         <v>56</v>
       </c>
       <c r="L16" s="155"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="159" t="inlineStr">
+        <is>
+          <t>※ 仕入先別の仕入高の内訳は未受領。上記は令和7年12月期の買掛金の内訳書に基づく期末残高であり、仕入高そのものではない。医薬品卸大手3社（㈱ﾒﾃﾞｨｾｵ・ｱﾙﾌﾚｯｻ㈱・㈱ｽｽﾞｹﾝ）で買掛金残高の99.3%を占める。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -30318,19 +30449,16 @@
       <c r="E7" s="61"/>
       <c r="F7" s="61"/>
       <c r="G7" s="100"/>
-      <c r="H7" s="59" t="e">
+      <c r="H7" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I7" s="100"/>
-      <c r="J7" s="59" t="e">
+      <c r="J7" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K7" s="100"/>
-      <c r="L7" s="59" t="e">
+      <c r="L7" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="M7" s="99"/>
     </row>
@@ -30343,19 +30471,16 @@
       <c r="E8" s="61"/>
       <c r="F8" s="61"/>
       <c r="G8" s="100"/>
-      <c r="H8" s="59" t="e">
+      <c r="H8" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I8" s="100"/>
-      <c r="J8" s="59" t="e">
+      <c r="J8" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K8" s="100"/>
-      <c r="L8" s="59" t="e">
+      <c r="L8" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="M8" s="99"/>
     </row>
@@ -30368,19 +30493,16 @@
       <c r="E9" s="61"/>
       <c r="F9" s="61"/>
       <c r="G9" s="100"/>
-      <c r="H9" s="59" t="e">
+      <c r="H9" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I9" s="100"/>
-      <c r="J9" s="59" t="e">
+      <c r="J9" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K9" s="100"/>
-      <c r="L9" s="59" t="e">
+      <c r="L9" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="M9" s="99"/>
     </row>
@@ -30393,19 +30515,16 @@
       <c r="E10" s="61"/>
       <c r="F10" s="61"/>
       <c r="G10" s="100"/>
-      <c r="H10" s="59" t="e">
+      <c r="H10" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I10" s="100"/>
-      <c r="J10" s="59" t="e">
+      <c r="J10" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K10" s="100"/>
-      <c r="L10" s="59" t="e">
+      <c r="L10" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="M10" s="99"/>
     </row>
@@ -30418,19 +30537,16 @@
       <c r="E11" s="61"/>
       <c r="F11" s="61"/>
       <c r="G11" s="100"/>
-      <c r="H11" s="59" t="e">
+      <c r="H11" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I11" s="100"/>
-      <c r="J11" s="59" t="e">
+      <c r="J11" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K11" s="100"/>
-      <c r="L11" s="59" t="e">
+      <c r="L11" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="M11" s="99"/>
     </row>
@@ -30443,19 +30559,16 @@
       <c r="E12" s="61"/>
       <c r="F12" s="61"/>
       <c r="G12" s="100"/>
-      <c r="H12" s="59" t="e">
+      <c r="H12" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I12" s="100"/>
-      <c r="J12" s="59" t="e">
+      <c r="J12" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K12" s="100"/>
-      <c r="L12" s="59" t="e">
+      <c r="L12" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="M12" s="99"/>
     </row>
@@ -30468,19 +30581,16 @@
       <c r="E13" s="61"/>
       <c r="F13" s="61"/>
       <c r="G13" s="100"/>
-      <c r="H13" s="59" t="e">
+      <c r="H13" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I13" s="100"/>
-      <c r="J13" s="59" t="e">
+      <c r="J13" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K13" s="100"/>
-      <c r="L13" s="59" t="e">
+      <c r="L13" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="M13" s="99"/>
     </row>
@@ -30493,19 +30603,16 @@
       <c r="E14" s="61"/>
       <c r="F14" s="61"/>
       <c r="G14" s="100"/>
-      <c r="H14" s="59" t="e">
+      <c r="H14" s="59">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="I14" s="100"/>
-      <c r="J14" s="59" t="e">
+      <c r="J14" s="59">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K14" s="100"/>
-      <c r="L14" s="59" t="e">
+      <c r="L14" s="59">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="M14" s="99"/>
     </row>
@@ -30621,49 +30728,35 @@
       <c r="B5" s="434">
         <v>1</v>
       </c>
-      <c r="C5" s="61" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="E5" s="112">
-        <v>12000000</v>
-      </c>
-      <c r="F5" s="16">
-        <v>700</v>
-      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="D5" s="61"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="59">
-        <f>F5/$F$15</f>
-        <v>0.7</v>
-      </c>
-      <c r="H5" s="98" t="s">
-        <v>112</v>
+        <f>IFERROR(F5/$F$15,"")</f>
+      </c>
+      <c r="H5" s="98" t="inlineStr">
+        <is>
+          <t>株主構成は未受領。短期借入金の相手先が「親会社 一般社団法人スタジオ技術研究会」と記載されており、資本関係の有無を含め要確認。</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="2:8" ht="23.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="435">
         <v>2</v>
       </c>
-      <c r="C6" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="61" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" s="112">
-        <v>10000000</v>
-      </c>
-      <c r="F6" s="16">
-        <v>300</v>
-      </c>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="112"/>
+      <c r="F6" s="16"/>
       <c r="G6" s="59">
-        <f t="shared" ref="G6:G15" si="0">F6/$F$15</f>
-        <v>0.3</v>
-      </c>
-      <c r="H6" s="99" t="s">
-        <v>113</v>
-      </c>
+        <f t="shared" ref="G6:G15" si="0">IFERROR(F6/$F$15,"")</f>
+      </c>
+      <c r="H6" s="99"/>
     </row>
     <row r="7" spans="2:8" ht="23.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="436">
@@ -30675,7 +30768,6 @@
       <c r="F7" s="16"/>
       <c r="G7" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="H7" s="99"/>
     </row>
@@ -30689,7 +30781,6 @@
       <c r="F8" s="16"/>
       <c r="G8" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="H8" s="99"/>
     </row>
@@ -30703,7 +30794,6 @@
       <c r="F9" s="16"/>
       <c r="G9" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="H9" s="99"/>
     </row>
@@ -30717,7 +30807,6 @@
       <c r="F10" s="16"/>
       <c r="G10" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="H10" s="99"/>
     </row>
@@ -30731,7 +30820,6 @@
       <c r="F11" s="16"/>
       <c r="G11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="H11" s="99"/>
     </row>
@@ -30745,7 +30833,6 @@
       <c r="F12" s="16"/>
       <c r="G12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="H12" s="99"/>
     </row>
@@ -30759,7 +30846,6 @@
       <c r="F13" s="16"/>
       <c r="G13" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="H13" s="99"/>
     </row>
@@ -30773,7 +30859,6 @@
       <c r="F14" s="16"/>
       <c r="G14" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="H14" s="99"/>
     </row>
@@ -30793,7 +30878,6 @@
       </c>
       <c r="G15" s="157">
         <f t="shared" si="0"/>
-        <v>1</v>
       </c>
       <c r="H15" s="155"/>
     </row>
@@ -30867,93 +30951,67 @@
       <c r="B5" s="434">
         <v>1</v>
       </c>
-      <c r="C5" s="61" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="E5" s="61" t="s">
-        <v>122</v>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>三河　太一</t>
+        </is>
+      </c>
+      <c r="D5" s="61" t="inlineStr">
+        <is>
+          <t>代表取締役</t>
+        </is>
+      </c>
+      <c r="E5" s="61" t="inlineStr">
+        <is>
+          <t>本人</t>
+        </is>
       </c>
       <c r="F5" s="112">
-        <v>12000000</v>
-      </c>
-      <c r="G5" s="114" t="s">
-        <v>116</v>
-      </c>
-      <c r="H5" s="98" t="s">
-        <v>112</v>
+        <v>11870000</v>
+      </c>
+      <c r="G5" s="114" t="inlineStr">
+        <is>
+          <t>常勤（役員給与等の内訳書による）</t>
+        </is>
+      </c>
+      <c r="H5" s="98" t="inlineStr">
+        <is>
+          <t>M&amp;A後の処遇は要確認</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="2:8" ht="23.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="435">
         <v>2</v>
       </c>
-      <c r="C6" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="61" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" s="61" t="s">
-        <v>123</v>
-      </c>
-      <c r="F6" s="112">
-        <v>10000000</v>
-      </c>
-      <c r="G6" s="115" t="s">
-        <v>115</v>
-      </c>
-      <c r="H6" s="99" t="s">
-        <v>120</v>
-      </c>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="99"/>
     </row>
     <row r="7" spans="2:8" ht="23.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="436">
         <v>3</v>
       </c>
-      <c r="C7" s="61" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7" s="61" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" s="112">
-        <v>5000000</v>
-      </c>
-      <c r="G7" s="115" t="s">
-        <v>119</v>
-      </c>
-      <c r="H7" s="99" t="s">
-        <v>129</v>
-      </c>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="115"/>
+      <c r="H7" s="99"/>
     </row>
     <row r="8" spans="2:8" ht="23.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="435">
         <v>4</v>
       </c>
-      <c r="C8" s="61" t="s">
-        <v>125</v>
-      </c>
-      <c r="D8" s="61" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="61" t="s">
-        <v>127</v>
-      </c>
-      <c r="F8" s="113" t="s">
-        <v>130</v>
-      </c>
-      <c r="G8" s="115" t="s">
-        <v>131</v>
-      </c>
-      <c r="H8" s="99" t="s">
-        <v>128</v>
-      </c>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="115"/>
+      <c r="H8" s="99"/>
     </row>
     <row r="9" spans="2:8" ht="23.45" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="94">
@@ -31034,6 +31092,13 @@
       </c>
       <c r="G15" s="154"/>
       <c r="H15" s="155"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="152" t="inlineStr">
+        <is>
+          <t>※ 令和7年12月期の役員給与等の内訳書による。上記以外に役員の計上はない。人件費の内訳上、従業員給与手当67,951千円のうち代表者及びその家族分が4,140千円ある（要確認）。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -31977,24 +32042,16 @@
       </c>
     </row>
     <row r="3" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="135" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="137" t="s">
-        <v>157</v>
-      </c>
-      <c r="D3" s="131">
-        <v>500</v>
-      </c>
-      <c r="E3" s="133">
-        <v>1000000</v>
-      </c>
-      <c r="F3" s="133">
-        <v>1000000</v>
-      </c>
-      <c r="G3" s="136" t="s">
-        <v>152</v>
-      </c>
+      <c r="B3" s="135" t="inlineStr">
+        <is>
+          <t>要確認（本社所在地の資料未受領）</t>
+        </is>
+      </c>
+      <c r="C3" s="137"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="133"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="136"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -32504,109 +32561,273 @@
       </c>
     </row>
     <row r="4" spans="2:10" ht="39" x14ac:dyDescent="0.35">
-      <c r="B4" s="446" t="s">
-        <v>194</v>
-      </c>
-      <c r="C4" s="61" t="s">
-        <v>188</v>
-      </c>
-      <c r="D4" s="60" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" s="142">
-        <v>500.12</v>
-      </c>
-      <c r="F4" s="137" t="s">
-        <v>157</v>
-      </c>
-      <c r="G4" s="60" t="s">
-        <v>189</v>
+      <c r="B4" s="446" t="inlineStr">
+        <is>
+          <t>①店舗</t>
+        </is>
+      </c>
+      <c r="C4" s="61" t="inlineStr">
+        <is>
+          <t>建物）店舗</t>
+        </is>
+      </c>
+      <c r="D4" s="60" t="inlineStr">
+        <is>
+          <t>横浜市緑区中山町305-20</t>
+        </is>
+      </c>
+      <c r="E4" s="142"/>
+      <c r="F4" s="137" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="G4" s="60" t="inlineStr">
+        <is>
+          <t>㈱ｲｴﾛｰｽﾀｼﾞｵ</t>
+        </is>
       </c>
       <c r="H4" s="133">
-        <v>3000000</v>
+        <v>337500</v>
       </c>
       <c r="I4" s="133">
-        <v>5000000</v>
-      </c>
-      <c r="J4" s="132" t="s">
-        <v>187</v>
+        <v>1000000</v>
+      </c>
+      <c r="J4" s="132" t="inlineStr">
+        <is>
+          <t>年額 4,050,000円（R7.2〜R8.1）</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="2:10" ht="39" x14ac:dyDescent="0.35">
-      <c r="B5" s="446" t="s">
-        <v>193</v>
-      </c>
-      <c r="C5" s="61" t="s">
-        <v>191</v>
-      </c>
-      <c r="D5" s="60" t="s">
-        <v>169</v>
-      </c>
-      <c r="E5" s="142">
-        <v>500.12</v>
-      </c>
-      <c r="F5" s="137" t="s">
-        <v>157</v>
-      </c>
-      <c r="G5" s="60" t="s">
-        <v>189</v>
+      <c r="B5" s="446" t="inlineStr">
+        <is>
+          <t>②店舗</t>
+        </is>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>建物）店舗</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="inlineStr">
+        <is>
+          <t>横浜市都筑区仲町台1-33-16</t>
+        </is>
+      </c>
+      <c r="E5" s="142"/>
+      <c r="F5" s="137" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="G5" s="60" t="inlineStr">
+        <is>
+          <t>片桐　昇</t>
+        </is>
       </c>
       <c r="H5" s="133">
-        <v>3000000</v>
+        <v>296947</v>
       </c>
       <c r="I5" s="133">
-        <v>5000000</v>
-      </c>
-      <c r="J5" s="132" t="s">
-        <v>192</v>
+        <v>2000000</v>
+      </c>
+      <c r="J5" s="132" t="inlineStr">
+        <is>
+          <t>年額 3,563,364円（R7.2〜R8.1）</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="2:10" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
+      <c r="B6" s="61" t="inlineStr">
+        <is>
+          <t>③店舗</t>
+        </is>
+      </c>
+      <c r="C6" s="61" t="inlineStr">
+        <is>
+          <t>建物）店舗</t>
+        </is>
+      </c>
+      <c r="D6" s="61" t="inlineStr">
+        <is>
+          <t>横浜市都筑区仲町台1-2-28</t>
+        </is>
+      </c>
       <c r="E6" s="147"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="112"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="141"/>
+      <c r="F6" s="62" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="G6" s="61" t="inlineStr">
+        <is>
+          <t>㈱ﾚｰﾍﾞﾝﾄﾗｽﾄ</t>
+        </is>
+      </c>
+      <c r="H6" s="112">
+        <v>718025</v>
+      </c>
+      <c r="I6" s="112">
+        <v>3480000</v>
+      </c>
+      <c r="J6" s="141" t="inlineStr">
+        <is>
+          <t>年額 8,616,300円（R7.2〜R8.1）</t>
+        </is>
+      </c>
     </row>
     <row r="7" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="146"/>
-      <c r="C7" s="146"/>
-      <c r="D7" s="61"/>
+      <c r="B7" s="146" t="inlineStr">
+        <is>
+          <t>駐車場</t>
+        </is>
+      </c>
+      <c r="C7" s="146" t="inlineStr">
+        <is>
+          <t>土地）駐車場</t>
+        </is>
+      </c>
+      <c r="D7" s="61" t="inlineStr">
+        <is>
+          <t>横浜市都筑区仲町台2-11-1</t>
+        </is>
+      </c>
       <c r="E7" s="143"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="141"/>
+      <c r="F7" s="61" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="G7" s="61" t="inlineStr">
+        <is>
+          <t>西川　香代子</t>
+        </is>
+      </c>
+      <c r="H7" s="112">
+        <v>17600</v>
+      </c>
+      <c r="I7" s="112">
+        <v>17280</v>
+      </c>
+      <c r="J7" s="141" t="inlineStr">
+        <is>
+          <t>年額 211,200円（R7.2〜R8.1）</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="146"/>
-      <c r="C8" s="146"/>
-      <c r="D8" s="61"/>
+      <c r="B8" s="146" t="inlineStr">
+        <is>
+          <t>駐車場</t>
+        </is>
+      </c>
+      <c r="C8" s="146" t="inlineStr">
+        <is>
+          <t>土地）駐車場</t>
+        </is>
+      </c>
+      <c r="D8" s="61" t="inlineStr">
+        <is>
+          <t>横浜市都筑区仲町台5-6</t>
+        </is>
+      </c>
       <c r="E8" s="143"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="141"/>
+      <c r="F8" s="61" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="G8" s="61" t="inlineStr">
+        <is>
+          <t>㈱ﾘﾌﾞｸﾗｯｼｲ</t>
+        </is>
+      </c>
+      <c r="H8" s="112">
+        <v>17600</v>
+      </c>
+      <c r="I8" s="112">
+        <v>16000</v>
+      </c>
+      <c r="J8" s="141" t="inlineStr">
+        <is>
+          <t>年額 211,200円（R7.2〜R8.1）</t>
+        </is>
+      </c>
     </row>
     <row r="9" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="146"/>
-      <c r="C9" s="146"/>
-      <c r="D9" s="61"/>
+      <c r="B9" s="146" t="inlineStr">
+        <is>
+          <t>駐車場</t>
+        </is>
+      </c>
+      <c r="C9" s="146" t="inlineStr">
+        <is>
+          <t>土地）駐車場</t>
+        </is>
+      </c>
+      <c r="D9" s="61" t="inlineStr">
+        <is>
+          <t>横浜市都筑区仲町台1-14</t>
+        </is>
+      </c>
       <c r="E9" s="143"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="112"/>
+      <c r="F9" s="61" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="G9" s="61" t="inlineStr">
+        <is>
+          <t>㈱ﾘﾌﾞｸﾗｯｼｲ</t>
+        </is>
+      </c>
+      <c r="H9" s="112">
+        <v>18700</v>
+      </c>
       <c r="I9" s="112"/>
-      <c r="J9" s="141"/>
+      <c r="J9" s="141" t="inlineStr">
+        <is>
+          <t>年額 224,400円（R7.2〜R8.1）</t>
+        </is>
+      </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="G10" s="148"/>
+      <c r="B10" s="146" t="inlineStr">
+        <is>
+          <t>駐車場</t>
+        </is>
+      </c>
+      <c r="C10" s="146" t="inlineStr">
+        <is>
+          <t>土地）駐車場</t>
+        </is>
+      </c>
+      <c r="D10" s="61" t="inlineStr">
+        <is>
+          <t>横浜市都筑区仲町台</t>
+        </is>
+      </c>
+      <c r="E10" s="143"/>
+      <c r="F10" s="61" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="G10" s="148" t="inlineStr">
+        <is>
+          <t>神奈川中央住宅㈱</t>
+        </is>
+      </c>
+      <c r="H10" s="112">
+        <v>19067</v>
+      </c>
+      <c r="I10" s="112"/>
+      <c r="J10" s="141" t="inlineStr">
+        <is>
+          <t>年額 228,800円（R7.2〜R8.1）</t>
+        </is>
+      </c>
     </row>
     <row r="11" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="146"/>
@@ -32620,72 +32841,63 @@
       <c r="J11" s="141"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B12" s="146" t="inlineStr">
+        <is>
+          <t>※ 令和7年12月期の地代家賃等の内訳書及び差入保証金の内訳による。差入保証金にはほかにﾄｰｾｲ･ｺﾐｭﾆﾃｨ㈱126,000円があるが、地代家賃の内訳に対応する記載がなく内容は要確認。賃貸借契約書は未受領のため契約期間・更新条件・原状回復義務は要確認。</t>
+        </is>
+      </c>
+      <c r="C12" s="146"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="61"/>
       <c r="G12" s="148"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="141"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="148"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="141"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14" s="74"/>
       <c r="C14" s="74"/>
+      <c r="D14" s="134"/>
       <c r="E14" s="65"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="134"/>
       <c r="H14" s="65"/>
       <c r="I14" s="65"/>
+      <c r="J14" s="130"/>
     </row>
     <row r="15" spans="2:10" ht="39" x14ac:dyDescent="0.35">
-      <c r="B15" s="145" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="145" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="134" t="s">
-        <v>161</v>
-      </c>
-      <c r="E15" s="134" t="s">
-        <v>162</v>
-      </c>
-      <c r="F15" s="134" t="s">
-        <v>185</v>
-      </c>
-      <c r="G15" s="134" t="s">
-        <v>186</v>
-      </c>
-      <c r="H15" s="134" t="s">
-        <v>153</v>
-      </c>
-      <c r="I15" s="134" t="s">
-        <v>154</v>
-      </c>
-      <c r="J15" s="130" t="s">
-        <v>84</v>
-      </c>
+      <c r="B15" s="145"/>
+      <c r="C15" s="145"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="134"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="130"/>
     </row>
     <row r="16" spans="2:10" ht="39" x14ac:dyDescent="0.35">
-      <c r="B16" s="446" t="s">
-        <v>193</v>
-      </c>
-      <c r="C16" s="61" t="s">
-        <v>191</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>169</v>
-      </c>
-      <c r="E16" s="142">
-        <v>500.12</v>
-      </c>
-      <c r="F16" s="137" t="s">
-        <v>157</v>
-      </c>
-      <c r="G16" s="60" t="s">
-        <v>189</v>
-      </c>
-      <c r="H16" s="133">
-        <v>3000000</v>
-      </c>
-      <c r="I16" s="133">
-        <v>5000000</v>
-      </c>
-      <c r="J16" s="132" t="s">
-        <v>192</v>
-      </c>
+      <c r="B16" s="446"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="142"/>
+      <c r="F16" s="137"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="133"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="132"/>
     </row>
     <row r="17" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="61"/>
@@ -46688,14 +46900,12 @@
         <v>8.9416408969387115E-3</v>
       </c>
       <c r="I8" s="248"/>
-      <c r="J8" s="251" t="e">
+      <c r="J8" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K8" s="248"/>
-      <c r="L8" s="251" t="e">
+      <c r="L8" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -46720,14 +46930,12 @@
         <v>0</v>
       </c>
       <c r="I9" s="248"/>
-      <c r="J9" s="251" t="e">
+      <c r="J9" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K9" s="248"/>
-      <c r="L9" s="251" t="e">
+      <c r="L9" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -46756,14 +46964,12 @@
         <v>3.0324203229943884E-2</v>
       </c>
       <c r="I10" s="248"/>
-      <c r="J10" s="251" t="e">
+      <c r="J10" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K10" s="248"/>
-      <c r="L10" s="251" t="e">
+      <c r="L10" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -46792,14 +46998,12 @@
         <v>8.1490065245422346E-3</v>
       </c>
       <c r="I11" s="248"/>
-      <c r="J11" s="251" t="e">
+      <c r="J11" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K11" s="248"/>
-      <c r="L11" s="251" t="e">
+      <c r="L11" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -46828,14 +47032,12 @@
         <v>2.4808368706864678E-4</v>
       </c>
       <c r="I12" s="248"/>
-      <c r="J12" s="251" t="e">
+      <c r="J12" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K12" s="248"/>
-      <c r="L12" s="251" t="e">
+      <c r="L12" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -46864,14 +47066,12 @@
         <v>2.9454637742592389E-3</v>
       </c>
       <c r="I13" s="248"/>
-      <c r="J13" s="251" t="e">
+      <c r="J13" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K13" s="248"/>
-      <c r="L13" s="251" t="e">
+      <c r="L13" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="14" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -46900,14 +47100,12 @@
         <v>2.4254865193100469E-4</v>
       </c>
       <c r="I14" s="248"/>
-      <c r="J14" s="251" t="e">
+      <c r="J14" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K14" s="248"/>
-      <c r="L14" s="251" t="e">
+      <c r="L14" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="15" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -46936,14 +47134,12 @@
         <v>1.2853783594653138E-3</v>
       </c>
       <c r="I15" s="248"/>
-      <c r="J15" s="251" t="e">
+      <c r="J15" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K15" s="248"/>
-      <c r="L15" s="251" t="e">
+      <c r="L15" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="16" spans="2:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -46972,14 +47168,12 @@
         <v>7.7498854612719987E-3</v>
       </c>
       <c r="I16" s="248"/>
-      <c r="J16" s="251" t="e">
+      <c r="J16" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K16" s="248"/>
-      <c r="L16" s="251" t="e">
+      <c r="L16" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47008,14 +47202,12 @@
         <v>3.8246645299529155E-3</v>
       </c>
       <c r="I17" s="248"/>
-      <c r="J17" s="251" t="e">
+      <c r="J17" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K17" s="248"/>
-      <c r="L17" s="251" t="e">
+      <c r="L17" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47044,14 +47236,12 @@
         <v>8.7388947134482246E-3</v>
       </c>
       <c r="I18" s="248"/>
-      <c r="J18" s="251" t="e">
+      <c r="J18" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K18" s="248"/>
-      <c r="L18" s="251" t="e">
+      <c r="L18" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47080,14 +47270,12 @@
         <v>4.9544997317074214E-3</v>
       </c>
       <c r="I19" s="248"/>
-      <c r="J19" s="251" t="e">
+      <c r="J19" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K19" s="248"/>
-      <c r="L19" s="251" t="e">
+      <c r="L19" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47116,14 +47304,12 @@
         <v>1.4898614084537674E-3</v>
       </c>
       <c r="I20" s="248"/>
-      <c r="J20" s="251" t="e">
+      <c r="J20" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K20" s="248"/>
-      <c r="L20" s="251" t="e">
+      <c r="L20" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47152,14 +47338,12 @@
         <v>2.9016785417782954E-3</v>
       </c>
       <c r="I21" s="248"/>
-      <c r="J21" s="251" t="e">
+      <c r="J21" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K21" s="248"/>
-      <c r="L21" s="251" t="e">
+      <c r="L21" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47188,14 +47372,12 @@
         <v>4.7778344995350302E-4</v>
       </c>
       <c r="I22" s="248"/>
-      <c r="J22" s="251" t="e">
+      <c r="J22" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K22" s="248"/>
-      <c r="L22" s="251" t="e">
+      <c r="L22" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47224,14 +47406,12 @@
         <v>1.5979442269777899E-3</v>
       </c>
       <c r="I23" s="248"/>
-      <c r="J23" s="251" t="e">
+      <c r="J23" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K23" s="248"/>
-      <c r="L23" s="251" t="e">
+      <c r="L23" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47260,14 +47440,12 @@
         <v>2.7001929142941427E-2</v>
       </c>
       <c r="I24" s="248"/>
-      <c r="J24" s="251" t="e">
+      <c r="J24" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K24" s="248"/>
-      <c r="L24" s="251" t="e">
+      <c r="L24" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47296,14 +47474,12 @@
         <v>4.7841453905327951E-2</v>
       </c>
       <c r="I25" s="248"/>
-      <c r="J25" s="251" t="e">
+      <c r="J25" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K25" s="248"/>
-      <c r="L25" s="251" t="e">
+      <c r="L25" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47332,14 +47508,12 @@
         <v>3.1304133793865038E-4</v>
       </c>
       <c r="I26" s="248"/>
-      <c r="J26" s="251" t="e">
+      <c r="J26" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K26" s="248"/>
-      <c r="L26" s="251" t="e">
+      <c r="L26" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47368,14 +47542,12 @@
         <v>4.4846650285256104E-3</v>
       </c>
       <c r="I27" s="248"/>
-      <c r="J27" s="251" t="e">
+      <c r="J27" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K27" s="248"/>
-      <c r="L27" s="251" t="e">
+      <c r="L27" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47404,14 +47576,12 @@
         <v>4.0728796706099752E-4</v>
       </c>
       <c r="I28" s="248"/>
-      <c r="J28" s="251" t="e">
+      <c r="J28" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K28" s="248"/>
-      <c r="L28" s="251" t="e">
+      <c r="L28" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="29" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47440,14 +47610,12 @@
         <v>1.2650433284032923E-2</v>
       </c>
       <c r="I29" s="248"/>
-      <c r="J29" s="251" t="e">
+      <c r="J29" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K29" s="248"/>
-      <c r="L29" s="251" t="e">
+      <c r="L29" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="30" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47476,14 +47644,12 @@
         <v>1.6219918430027754E-3</v>
       </c>
       <c r="I30" s="248"/>
-      <c r="J30" s="251" t="e">
+      <c r="J30" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K30" s="248"/>
-      <c r="L30" s="251" t="e">
+      <c r="L30" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="31" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47512,14 +47678,12 @@
         <v>1.465567666561115E-3</v>
       </c>
       <c r="I31" s="248"/>
-      <c r="J31" s="251" t="e">
+      <c r="J31" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K31" s="248"/>
-      <c r="L31" s="251" t="e">
+      <c r="L31" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47548,14 +47712,12 @@
         <v>1.2182838885623853E-3</v>
       </c>
       <c r="I32" s="248"/>
-      <c r="J32" s="251" t="e">
+      <c r="J32" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K32" s="248"/>
-      <c r="L32" s="251" t="e">
+      <c r="L32" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="33" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47584,14 +47746,12 @@
         <v>7.9600210145622068E-3</v>
       </c>
       <c r="I33" s="248"/>
-      <c r="J33" s="251" t="e">
+      <c r="J33" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K33" s="248"/>
-      <c r="L33" s="251" t="e">
+      <c r="L33" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="34" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47620,14 +47780,12 @@
         <v>1.0363375783976265E-2</v>
       </c>
       <c r="I34" s="248"/>
-      <c r="J34" s="251" t="e">
+      <c r="J34" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K34" s="248"/>
-      <c r="L34" s="251" t="e">
+      <c r="L34" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="35" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47648,14 +47806,12 @@
         <v>0</v>
       </c>
       <c r="I35" s="248"/>
-      <c r="J35" s="251" t="e">
+      <c r="J35" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K35" s="248"/>
-      <c r="L35" s="251" t="e">
+      <c r="L35" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47676,14 +47832,12 @@
         <v>0</v>
       </c>
       <c r="I36" s="248"/>
-      <c r="J36" s="251" t="e">
+      <c r="J36" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K36" s="248"/>
-      <c r="L36" s="251" t="e">
+      <c r="L36" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="37" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47704,14 +47858,12 @@
         <v>0</v>
       </c>
       <c r="I37" s="248"/>
-      <c r="J37" s="251" t="e">
+      <c r="J37" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K37" s="248"/>
-      <c r="L37" s="251" t="e">
+      <c r="L37" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="38" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47732,14 +47884,12 @@
         <v>0</v>
       </c>
       <c r="I38" s="248"/>
-      <c r="J38" s="251" t="e">
+      <c r="J38" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K38" s="248"/>
-      <c r="L38" s="251" t="e">
+      <c r="L38" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="39" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -47760,14 +47910,12 @@
         <v>0</v>
       </c>
       <c r="I39" s="248"/>
-      <c r="J39" s="251" t="e">
+      <c r="J39" s="251">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
       </c>
       <c r="K39" s="248"/>
-      <c r="L39" s="251" t="e">
+      <c r="L39" s="251">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="40" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/株式会社ミドリメディカル/株式会社ミドリメディカル_案件マスター_260819.xlsx
+++ b/株式会社ミドリメディカル/株式会社ミドリメディカル_案件マスター_260819.xlsx
@@ -23355,7 +23355,9 @@
         <f>SGA!C6</f>
         <v>10500000</v>
       </c>
-      <c r="D5" s="234"/>
+      <c r="D5" s="234">
+        <f>-C5</f>
+      </c>
       <c r="E5" s="263">
         <f>C5+D5</f>
         <v>10500000</v>
@@ -23364,7 +23366,9 @@
         <f>SGA!E6</f>
         <v>17120000</v>
       </c>
-      <c r="G5" s="234"/>
+      <c r="G5" s="234">
+        <f>-F5</f>
+      </c>
       <c r="H5" s="263">
         <f>F5+G5</f>
         <v>17120000</v>
@@ -23373,7 +23377,9 @@
         <f>SGA!G6</f>
         <v>11870000</v>
       </c>
-      <c r="J5" s="234"/>
+      <c r="J5" s="234">
+        <f>-I5</f>
+      </c>
       <c r="K5" s="263">
         <f>I5+J5</f>
         <v>11870000</v>
@@ -23406,7 +23412,9 @@
         <f>SGA!C7</f>
         <v>64348988</v>
       </c>
-      <c r="D6" s="234"/>
+      <c r="D6" s="234">
+        <v>-4140000</v>
+      </c>
       <c r="E6" s="263">
         <f t="shared" ref="E6:E38" si="0">C6+D6</f>
         <v>64348988</v>
@@ -23415,7 +23423,9 @@
         <f>SGA!E7</f>
         <v>65194441</v>
       </c>
-      <c r="G6" s="234"/>
+      <c r="G6" s="234">
+        <v>-4140000</v>
+      </c>
       <c r="H6" s="263">
         <f t="shared" ref="H6:H38" si="1">F6+G6</f>
         <v>65194441</v>
@@ -23424,7 +23434,9 @@
         <f>SGA!G7</f>
         <v>64753816</v>
       </c>
-      <c r="J6" s="234"/>
+      <c r="J6" s="234">
+        <v>-4140000</v>
+      </c>
       <c r="K6" s="263">
         <f t="shared" ref="K6:K34" si="2">I6+J6</f>
         <v>64753816</v>
@@ -23561,7 +23573,9 @@
         <f>SGA!C10</f>
         <v>11424051</v>
       </c>
-      <c r="D9" s="234"/>
+      <c r="D9" s="234">
+        <f>ROUND((D5+D6+D35)*0.15,0)</f>
+      </c>
       <c r="E9" s="263">
         <f t="shared" si="0"/>
         <v>11424051</v>
@@ -23570,7 +23584,9 @@
         <f>SGA!E10</f>
         <v>12207732</v>
       </c>
-      <c r="G9" s="234"/>
+      <c r="G9" s="234">
+        <f>ROUND((G5+G6+G35)*0.15,0)</f>
+      </c>
       <c r="H9" s="263">
         <f t="shared" si="1"/>
         <v>12207732</v>
@@ -23579,7 +23595,9 @@
         <f>SGA!G10</f>
         <v>10842135</v>
       </c>
-      <c r="J9" s="234"/>
+      <c r="J9" s="234">
+        <f>ROUND((J5+J6+J35)*0.15,0)</f>
+      </c>
       <c r="K9" s="263">
         <f t="shared" si="2"/>
         <v>10842135</v>
@@ -24885,21 +24903,31 @@
       </c>
     </row>
     <row r="35" spans="2:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="207"/>
+      <c r="B35" s="207" t="inlineStr">
+        <is>
+          <t>新任役員報酬（想定）</t>
+        </is>
+      </c>
       <c r="C35" s="268"/>
-      <c r="D35" s="234"/>
+      <c r="D35" s="234">
+        <v>10000000</v>
+      </c>
       <c r="E35" s="263">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F35" s="268"/>
-      <c r="G35" s="234"/>
+      <c r="G35" s="234">
+        <v>10000000</v>
+      </c>
       <c r="H35" s="263">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I35" s="268"/>
-      <c r="J35" s="234"/>
+      <c r="J35" s="234">
+        <v>10000000</v>
+      </c>
       <c r="K35" s="263">
         <f t="shared" ref="K35:K38" si="6">I35+J35</f>
         <v>0</v>
@@ -27524,7 +27552,7 @@
       </c>
       <c r="C9" s="62" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>一般社団法人スタジオ技術研究会（持株会社）</t>
         </is>
       </c>
     </row>
@@ -27534,7 +27562,7 @@
       </c>
       <c r="C10" s="61" t="inlineStr">
         <is>
-          <t>調剤薬局の運営</t>
+          <t>調剤薬局の運営（なかまち薬局・町の薬局・緑野薬局の3店舗）</t>
         </is>
       </c>
     </row>
@@ -27544,7 +27572,7 @@
       </c>
       <c r="C11" s="61" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>18名程度（薬剤師5名・時短1名・パート6名・事務6名／代表者及び配偶者を含む）</t>
         </is>
       </c>
     </row>
@@ -27574,7 +27602,7 @@
       </c>
       <c r="C14" s="61" t="inlineStr">
         <is>
-          <t>18,551千円（令和7年12月期・修正後EBITDA）</t>
+          <t>25,463千円（令和7年12月期・オーナー人件費正常化後のEBITDA）</t>
         </is>
       </c>
     </row>
@@ -27584,7 +27612,7 @@
       </c>
       <c r="C15" s="61" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>代表者の引退（山梨県の別荘で配偶者と生活したい意向）。2027年6月までの成約を希望</t>
         </is>
       </c>
     </row>
@@ -30730,10 +30758,14 @@
       </c>
       <c r="C5" s="61" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>一般社団法人スタジオ技術研究会</t>
         </is>
       </c>
-      <c r="D5" s="61"/>
+      <c r="D5" s="61" t="inlineStr">
+        <is>
+          <t>持株会社</t>
+        </is>
+      </c>
       <c r="E5" s="112"/>
       <c r="F5" s="16"/>
       <c r="G5" s="59">
@@ -30741,7 +30773,7 @@
       </c>
       <c r="H5" s="98" t="inlineStr">
         <is>
-          <t>株主構成は未受領。短期借入金の相手先が「親会社 一般社団法人スタジオ技術研究会」と記載されており、資本関係の有無を含め要確認。</t>
+          <t>面談議事録によれば、相続対策のために設立した社団法人が全株式を保有。借入金の内訳書上も「親会社」と記載されている。持分・議決権の状況及び社団法人自体の譲渡か対象会社株式の譲渡かは要確認。</t>
         </is>
       </c>
     </row>
@@ -30976,7 +31008,7 @@
       </c>
       <c r="H5" s="98" t="inlineStr">
         <is>
-          <t>M&amp;A後の処遇は要確認</t>
+          <t>M&amp;A時に退任予定（引継ぎ期間3〜6ヶ月を希望）</t>
         </is>
       </c>
     </row>
@@ -31096,7 +31128,7 @@
     <row r="16">
       <c r="C16" s="152" t="inlineStr">
         <is>
-          <t>※ 令和7年12月期の役員給与等の内訳書による。上記以外に役員の計上はない。人件費の内訳上、従業員給与手当67,951千円のうち代表者及びその家族分が4,140千円ある（要確認）。</t>
+          <t>※ 令和7年12月期の役員給与等の内訳書による。上記以外に役員の計上はない。人件費の内訳上、従業員給与手当67,951千円のうち代表者及びその家族分が4,140千円あり、配偶者（緑野薬局の事務担当）に係るものと認められる。代表者・配偶者ともにM&amp;A時に退任予定であり、合計16,010千円を正常収益力の算定上控除している。令和5年・6年12月期の家族分は内訳書が未受領のため、令和7年12月期と同額と仮定している（要確認）。</t>
         </is>
       </c>
     </row>
